--- a/Comparativa de Hipótesis.xlsx
+++ b/Comparativa de Hipótesis.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
   <si>
     <t>Hipótesis</t>
   </si>
@@ -284,9 +284,6 @@
     <t>La participación política afecta positivamente al SWB. La polarización afecta a los incentivos para la participación o el interés en la política</t>
   </si>
   <si>
-    <t>Datos propios</t>
-  </si>
-  <si>
     <t xml:space="preserve">La relación entre participación y SWB es más clara. La de polarización y participación no lo es tanto. Pero la polarización individual (ideológica) sí. </t>
   </si>
   <si>
@@ -294,9 +291,6 @@
   </si>
   <si>
     <t>H5</t>
-  </si>
-  <si>
-    <t>La polarización destruye la confianza social y eso afecta al SWB. La confianza social ayuda a mitigar el efecto de la caída de la confianza institucional</t>
   </si>
   <si>
     <t>La idea es que la polarización hace ver a las instituciones como agentes del otro bando y por eso se pierde la confianza. El otro se ve como un enemigo y se pierde la confianza social. Lee (2022); Brady &amp; Kent (2022)</t>
@@ -306,9 +300,6 @@
 H5.B:  Glatz &amp; Schwerdtfeger (2022)</t>
   </si>
   <si>
-    <t>Polarización disminuye confianza. Confianza aumenta SWB y mitiga el efecto,</t>
-  </si>
-  <si>
     <t>La idea es que el mecanismo de la confianza social es más importante que el mecanismo de la confianza insitucional. La intervención de política conviene por este canal</t>
   </si>
   <si>
@@ -325,6 +316,33 @@
   </si>
   <si>
     <t>Yo sí encuentro un vínculo directo negativo.</t>
+  </si>
+  <si>
+    <t>No se observa el vínculo con la base a nivel país</t>
+  </si>
+  <si>
+    <t>Datos propios multilevel</t>
+  </si>
+  <si>
+    <t>Granger a nivel país</t>
+  </si>
+  <si>
+    <t>La evidencia no respalda la hipótesis</t>
+  </si>
+  <si>
+    <t>La evidencia apunta a que la participación anticipa felicidad, pero no al revés</t>
+  </si>
+  <si>
+    <t>Polarización disminuye confianza. Confianza aumenta SWB y mitiga el efecto.</t>
+  </si>
+  <si>
+    <t>La polarización afecta negativamente la confianza social y eso afecta al SWB. La confianza social ayuda a mitigar el efecto de la caída de la confianza institucional</t>
+  </si>
+  <si>
+    <t>La evidencia sostiene H5A pero no H5B</t>
+  </si>
+  <si>
+    <t>Sí se observa una anticipación débil de polarización a caída en la confianza en las instituciones, pero no de confianza a felicidad</t>
   </si>
 </sst>
 </file>
@@ -682,18 +700,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
     <col min="2" max="2" width="37.5703125" customWidth="1"/>
     <col min="3" max="3" width="33.85546875" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" customWidth="1"/>
-    <col min="5" max="5" width="51.7109375" customWidth="1"/>
-    <col min="6" max="6" width="39.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="51.7109375" customWidth="1"/>
+    <col min="7" max="7" width="39.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1">
+    <row r="1" spans="1:7" ht="19.5" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -702,36 +721,42 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="66" customHeight="1">
+    <row r="2" spans="1:7" ht="66" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="77.25" customHeight="1">
+    <row r="3" spans="1:7" ht="77.25" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -745,13 +770,16 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="67.5" customHeight="1">
+    <row r="4" spans="1:7" ht="67.5" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -765,13 +793,16 @@
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="81" customHeight="1">
+      <c r="G4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="81" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -782,41 +813,48 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="69" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="69" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -920,12 +958,12 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
